--- a/modelo_preenchido.xlsx
+++ b/modelo_preenchido.xlsx
@@ -3947,7 +3947,7 @@
     <col width="32.1640625" bestFit="1" customWidth="1" min="11" max="11"/>
     <col width="25.83203125" customWidth="1" min="12" max="12"/>
     <col width="3.6640625" customWidth="1" min="13" max="13"/>
-    <col hidden="1" width="13" customWidth="1" min="14" max="14"/>
+    <col hidden="1" min="14" max="14"/>
     <col hidden="1" width="8.83203125" customWidth="1" min="15" max="16384"/>
   </cols>
   <sheetData>
@@ -6151,8 +6151,9 @@
       <c r="D91" s="250" t="n">
         <v>3102978.5</v>
       </c>
-      <c r="E91" s="250" t="n">
-        <v>2627506.52</v>
+      <c r="E91" s="250">
+        <f>IFERROR(VLOOKUP($B$91,#REF!,6,0)*-1,0)</f>
+        <v/>
       </c>
       <c r="F91" s="250">
         <f>IFERROR(VLOOKUP($B$91,#REF!,6,0)*-1,0)</f>
@@ -6195,8 +6196,9 @@
       <c r="D92" s="256" t="n">
         <v>736843.98</v>
       </c>
-      <c r="E92" s="256" t="n">
-        <v>554881.52</v>
+      <c r="E92" s="256">
+        <f>IFERROR(VLOOKUP($B$92,#REF!,6,0),0)</f>
+        <v/>
       </c>
       <c r="F92" s="256">
         <f>IFERROR(VLOOKUP($B$92,#REF!,6,0),0)</f>
@@ -6239,8 +6241,9 @@
       <c r="D93" s="256" t="n">
         <v>13736.81</v>
       </c>
-      <c r="E93" s="256" t="n">
-        <v>12574.16</v>
+      <c r="E93" s="256">
+        <f>IFERROR(VLOOKUP($B$93,#REF!,6,0)*-1,0)</f>
+        <v/>
       </c>
       <c r="F93" s="256">
         <f>IFERROR(VLOOKUP($B$93,#REF!,6,0)*-1,0)</f>
@@ -6284,8 +6287,9 @@
         <f>IFERROR((VLOOKUP($B$94,#REF!,6,0)*-1)-D95,0)</f>
         <v/>
       </c>
-      <c r="E94" s="256" t="n">
-        <v>242409.14</v>
+      <c r="E94" s="256">
+        <f>IFERROR((VLOOKUP($B$94,#REF!,6,0)*-1)-E95,0)</f>
+        <v/>
       </c>
       <c r="F94" s="256">
         <f>IFERROR((VLOOKUP($B$94,#REF!,6,0)*-1)-F95,0)</f>
@@ -6363,8 +6367,9 @@
       <c r="D96" s="258" t="n">
         <v>232519.77</v>
       </c>
-      <c r="E96" s="258" t="n">
-        <v>178010.62</v>
+      <c r="E96" s="258">
+        <f>IFERROR(VLOOKUP($B$96,#REF!,6,0),0)</f>
+        <v/>
       </c>
       <c r="F96" s="258">
         <f>IFERROR(VLOOKUP($B$96,#REF!,6,0),0)</f>
@@ -6403,8 +6408,9 @@
       <c r="D97" s="256" t="n">
         <v>1678159.06</v>
       </c>
-      <c r="E97" s="256" t="n">
-        <v>1415075.36</v>
+      <c r="E97" s="256">
+        <f>IFERROR(VLOOKUP($B$97,#REF!,6,0),0)</f>
+        <v/>
       </c>
       <c r="F97" s="256">
         <f>IFERROR(VLOOKUP($B$97,#REF!,6,0),0)</f>
@@ -6662,8 +6668,9 @@
       <c r="D105" s="256" t="n">
         <v>2921910.98</v>
       </c>
-      <c r="E105" s="256" t="n">
-        <v>6369494.4</v>
+      <c r="E105" s="256">
+        <f>IFERROR(VLOOKUP(B105,#REF!,7,0),0)</f>
+        <v/>
       </c>
       <c r="F105" s="256">
         <f>IFERROR(VLOOKUP(B105,#REF!,7,0),0)</f>
@@ -6863,8 +6870,9 @@
       <c r="D113" s="284" t="n">
         <v>0</v>
       </c>
-      <c r="E113" s="256" t="n">
-        <v>0</v>
+      <c r="E113" s="256">
+        <f>D116</f>
+        <v/>
       </c>
       <c r="F113" s="256">
         <f>E116</f>
@@ -6939,8 +6947,9 @@
       <c r="D115" s="268" t="n">
         <v>50000</v>
       </c>
-      <c r="E115" s="268" t="n">
-        <v>100000</v>
+      <c r="E115" s="268">
+        <f>IFERROR(VLOOKUP(B115,#REF!,6,0),0)</f>
+        <v/>
       </c>
       <c r="F115" s="268">
         <f>IFERROR(VLOOKUP(B115,#REF!,6,0),0)</f>

--- a/modelo_preenchido.xlsx
+++ b/modelo_preenchido.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17540" tabRatio="728" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17480" tabRatio="728" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instruções" sheetId="1" state="visible" r:id="rId1"/>
@@ -6151,13 +6151,11 @@
       <c r="D91" s="250" t="n">
         <v>3102978.5</v>
       </c>
-      <c r="E91" s="250">
-        <f>IFERROR(VLOOKUP($B$91,#REF!,6,0)*-1,0)</f>
-        <v/>
-      </c>
-      <c r="F91" s="250">
-        <f>IFERROR(VLOOKUP($B$91,#REF!,6,0)*-1,0)</f>
-        <v/>
+      <c r="E91" s="250" t="n">
+        <v>2627506.52</v>
+      </c>
+      <c r="F91" s="250" t="n">
+        <v>4861666.72</v>
       </c>
       <c r="G91" s="251">
         <f>SUM(D91:F91)</f>
@@ -6196,13 +6194,11 @@
       <c r="D92" s="256" t="n">
         <v>736843.98</v>
       </c>
-      <c r="E92" s="256">
-        <f>IFERROR(VLOOKUP($B$92,#REF!,6,0),0)</f>
-        <v/>
-      </c>
-      <c r="F92" s="256">
-        <f>IFERROR(VLOOKUP($B$92,#REF!,6,0),0)</f>
-        <v/>
+      <c r="E92" s="256" t="n">
+        <v>554881.52</v>
+      </c>
+      <c r="F92" s="256" t="n">
+        <v>1170558.79</v>
       </c>
       <c r="G92" s="257">
         <f>SUM(D92:F92)</f>
@@ -6241,13 +6237,11 @@
       <c r="D93" s="256" t="n">
         <v>13736.81</v>
       </c>
-      <c r="E93" s="256">
-        <f>IFERROR(VLOOKUP($B$93,#REF!,6,0)*-1,0)</f>
-        <v/>
-      </c>
-      <c r="F93" s="256">
-        <f>IFERROR(VLOOKUP($B$93,#REF!,6,0)*-1,0)</f>
-        <v/>
+      <c r="E93" s="256" t="n">
+        <v>12574.16</v>
+      </c>
+      <c r="F93" s="256" t="n">
+        <v>8079.5</v>
       </c>
       <c r="G93" s="257">
         <f>SUM(D93:F93)</f>
@@ -6287,13 +6281,11 @@
         <f>IFERROR((VLOOKUP($B$94,#REF!,6,0)*-1)-D95,0)</f>
         <v/>
       </c>
-      <c r="E94" s="256">
-        <f>IFERROR((VLOOKUP($B$94,#REF!,6,0)*-1)-E95,0)</f>
-        <v/>
-      </c>
-      <c r="F94" s="256">
-        <f>IFERROR((VLOOKUP($B$94,#REF!,6,0)*-1)-F95,0)</f>
-        <v/>
+      <c r="E94" s="256" t="n">
+        <v>242409.14</v>
+      </c>
+      <c r="F94" s="256" t="n">
+        <v>0</v>
       </c>
       <c r="G94" s="257">
         <f>SUM(D94:F94)</f>
@@ -6367,13 +6359,11 @@
       <c r="D96" s="258" t="n">
         <v>232519.77</v>
       </c>
-      <c r="E96" s="258">
-        <f>IFERROR(VLOOKUP($B$96,#REF!,6,0),0)</f>
-        <v/>
-      </c>
-      <c r="F96" s="258">
-        <f>IFERROR(VLOOKUP($B$96,#REF!,6,0),0)</f>
-        <v/>
+      <c r="E96" s="258" t="n">
+        <v>178010.62</v>
+      </c>
+      <c r="F96" s="258" t="n">
+        <v>927997.51</v>
       </c>
       <c r="G96" s="257">
         <f>SUM(D96:F96)</f>
@@ -6408,13 +6398,11 @@
       <c r="D97" s="256" t="n">
         <v>1678159.06</v>
       </c>
-      <c r="E97" s="256">
-        <f>IFERROR(VLOOKUP($B$97,#REF!,6,0),0)</f>
-        <v/>
-      </c>
-      <c r="F97" s="256">
-        <f>IFERROR(VLOOKUP($B$97,#REF!,6,0),0)</f>
-        <v/>
+      <c r="E97" s="256" t="n">
+        <v>1415075.36</v>
+      </c>
+      <c r="F97" s="256" t="n">
+        <v>2650275.19</v>
       </c>
       <c r="G97" s="257">
         <f>SUM(D97:F97)</f>
@@ -6668,13 +6656,11 @@
       <c r="D105" s="256" t="n">
         <v>2921910.98</v>
       </c>
-      <c r="E105" s="256">
-        <f>IFERROR(VLOOKUP(B105,#REF!,7,0),0)</f>
-        <v/>
-      </c>
-      <c r="F105" s="256">
-        <f>IFERROR(VLOOKUP(B105,#REF!,7,0),0)</f>
-        <v/>
+      <c r="E105" s="256" t="n">
+        <v>6369494.4</v>
+      </c>
+      <c r="F105" s="256" t="n">
+        <v>6061532.9</v>
       </c>
       <c r="G105" s="266">
         <f>F105</f>
@@ -6870,13 +6856,11 @@
       <c r="D113" s="284" t="n">
         <v>0</v>
       </c>
-      <c r="E113" s="256">
-        <f>D116</f>
-        <v/>
-      </c>
-      <c r="F113" s="256">
-        <f>E116</f>
-        <v/>
+      <c r="E113" s="256" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="256" t="n">
+        <v>0</v>
       </c>
       <c r="G113" s="256">
         <f>D113</f>
@@ -6947,13 +6931,11 @@
       <c r="D115" s="268" t="n">
         <v>50000</v>
       </c>
-      <c r="E115" s="268">
-        <f>IFERROR(VLOOKUP(B115,#REF!,6,0),0)</f>
-        <v/>
-      </c>
-      <c r="F115" s="268">
-        <f>IFERROR(VLOOKUP(B115,#REF!,6,0),0)</f>
-        <v/>
+      <c r="E115" s="268" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F115" s="268" t="n">
+        <v>100000</v>
       </c>
       <c r="G115" s="269">
         <f>SUM(D115:F115)</f>

--- a/modelo_preenchido.xlsx
+++ b/modelo_preenchido.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17480" tabRatio="728" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17440" tabRatio="728" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instruções" sheetId="1" state="visible" r:id="rId1"/>
@@ -4128,17 +4128,14 @@
           <t>Receita</t>
         </is>
       </c>
-      <c r="D17" s="250">
-        <f>IFERROR(VLOOKUP($B$17,#REF!,6,0)*-1,0)</f>
-        <v/>
-      </c>
-      <c r="E17" s="250">
-        <f>IFERROR(VLOOKUP($B$17,#REF!,6,0)*-1,0)</f>
-        <v/>
-      </c>
-      <c r="F17" s="250">
-        <f>IFERROR(VLOOKUP($B$17,#REF!,6,0)*-1,0)</f>
-        <v/>
+      <c r="D17" s="250" t="n">
+        <v>2627506.52</v>
+      </c>
+      <c r="E17" s="250" t="n">
+        <v>3102978.5</v>
+      </c>
+      <c r="F17" s="250" t="n">
+        <v>4861666.72</v>
       </c>
       <c r="G17" s="251">
         <f>SUM(D17:F17)</f>
@@ -4174,17 +4171,14 @@
           <t>Deduções</t>
         </is>
       </c>
-      <c r="D18" s="256">
-        <f>IFERROR(VLOOKUP($B$18,#REF!,6,0),0)</f>
-        <v/>
-      </c>
-      <c r="E18" s="256">
-        <f>IFERROR(VLOOKUP($B$18,#REF!,6,0),0)</f>
-        <v/>
-      </c>
-      <c r="F18" s="256">
-        <f>IFERROR(VLOOKUP($B$18,#REF!,6,0),0)</f>
-        <v/>
+      <c r="D18" s="256" t="n">
+        <v>554881.52</v>
+      </c>
+      <c r="E18" s="256" t="n">
+        <v>736843.98</v>
+      </c>
+      <c r="F18" s="256" t="n">
+        <v>1170558.79</v>
       </c>
       <c r="G18" s="257">
         <f>SUM(D18:F18)</f>
@@ -4220,12 +4214,15 @@
           <t>Receita Oper.</t>
         </is>
       </c>
-      <c r="D19" s="256" t="n"/>
-      <c r="E19" s="256">
-        <f>IFERROR(VLOOKUP($B$19,#REF!,6,0)*-1,0)</f>
-        <v/>
-      </c>
-      <c r="F19" s="256" t="n"/>
+      <c r="D19" s="256" t="n">
+        <v>12574.16</v>
+      </c>
+      <c r="E19" s="256" t="n">
+        <v>13736.81</v>
+      </c>
+      <c r="F19" s="256" t="n">
+        <v>8079.5</v>
+      </c>
       <c r="G19" s="257">
         <f>SUM(D19:F19)</f>
         <v/>
@@ -4260,17 +4257,15 @@
           <t>Outras Receitas</t>
         </is>
       </c>
-      <c r="D20" s="256">
-        <f>IFERROR((VLOOKUP($B$20,#REF!,6,0)*-1)-D21,0)</f>
-        <v/>
+      <c r="D20" s="256" t="n">
+        <v>242409.14</v>
       </c>
       <c r="E20" s="256">
         <f>IFERROR((VLOOKUP($B$20,#REF!,6,0)*-1)-E21,0)</f>
         <v/>
       </c>
-      <c r="F20" s="256">
-        <f>IFERROR((VLOOKUP($B$20,#REF!,6,0)*-1)-F21,0)</f>
-        <v/>
+      <c r="F20" s="256" t="n">
+        <v>0</v>
       </c>
       <c r="G20" s="257">
         <f>SUM(D20:F20)</f>
@@ -4341,9 +4336,15 @@
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D22" s="258" t="n"/>
-      <c r="E22" s="258" t="n"/>
-      <c r="F22" s="258" t="n"/>
+      <c r="D22" s="258" t="n">
+        <v>178010.62</v>
+      </c>
+      <c r="E22" s="258" t="n">
+        <v>232519.77</v>
+      </c>
+      <c r="F22" s="258" t="n">
+        <v>927997.51</v>
+      </c>
       <c r="G22" s="257">
         <f>SUM(D22:F22)</f>
         <v/>
@@ -4375,15 +4376,15 @@
           <t>CMV</t>
         </is>
       </c>
-      <c r="D23" s="256">
-        <f>IFERROR(VLOOKUP($B$23,#REF!,6,0),0)</f>
-        <v/>
-      </c>
-      <c r="E23" s="256">
-        <f>IFERROR(VLOOKUP($B$23,#REF!,6,0),0)</f>
-        <v/>
-      </c>
-      <c r="F23" s="256" t="n"/>
+      <c r="D23" s="256" t="n">
+        <v>1415075.36</v>
+      </c>
+      <c r="E23" s="256" t="n">
+        <v>1678159.06</v>
+      </c>
+      <c r="F23" s="256" t="n">
+        <v>2650275.19</v>
+      </c>
       <c r="G23" s="257">
         <f>SUM(D23:F23)</f>
         <v/>
@@ -4583,7 +4584,7 @@
         </is>
       </c>
       <c r="J29" s="142" t="n">
-        <v>0</v>
+        <v>1893.23</v>
       </c>
       <c r="K29" s="121" t="inlineStr">
         <is>
@@ -4639,17 +4640,14 @@
           <t>Estoque Contábil</t>
         </is>
       </c>
-      <c r="D31" s="256">
-        <f>IFERROR(VLOOKUP($B$31,#REF!,7,0),0)</f>
-        <v/>
-      </c>
-      <c r="E31" s="256">
-        <f>IFERROR(VLOOKUP(B31,#REF!,7,0),0)</f>
-        <v/>
-      </c>
-      <c r="F31" s="256">
-        <f>IFERROR(VLOOKUP(B31,#REF!,7,0),0)</f>
-        <v/>
+      <c r="D31" s="256" t="n">
+        <v>6369494.4</v>
+      </c>
+      <c r="E31" s="256" t="n">
+        <v>2921910.98</v>
+      </c>
+      <c r="F31" s="256" t="n">
+        <v>6061532.9</v>
       </c>
       <c r="G31" s="266">
         <f>F31</f>
@@ -4843,17 +4841,14 @@
           <t>Lucro/Prejuízo Acumulado</t>
         </is>
       </c>
-      <c r="D39" s="256">
-        <f>IFERROR(VLOOKUP($B$39,#REF!,3,0)*-1,0)</f>
-        <v/>
-      </c>
-      <c r="E39" s="256">
-        <f>D42</f>
-        <v/>
-      </c>
-      <c r="F39" s="256">
-        <f>E42</f>
-        <v/>
+      <c r="D39" s="256" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="256" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="256" t="n">
+        <v>0</v>
       </c>
       <c r="G39" s="266">
         <f>D39</f>
@@ -4921,17 +4916,14 @@
           <t>(-) Lucro distribuído no período</t>
         </is>
       </c>
-      <c r="D41" s="268">
-        <f>IFERROR(VLOOKUP($B$41,#REF!,6,0),0)</f>
-        <v/>
-      </c>
-      <c r="E41" s="268">
-        <f>IFERROR(VLOOKUP(B41,#REF!,6,0),0)</f>
-        <v/>
-      </c>
-      <c r="F41" s="268">
-        <f>IFERROR(VLOOKUP(B41,#REF!,6,0),0)</f>
-        <v/>
+      <c r="D41" s="268" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E41" s="268" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F41" s="268" t="n">
+        <v>100000</v>
       </c>
       <c r="G41" s="269">
         <f>SUM(D41:F41)</f>
@@ -5151,17 +5143,14 @@
           <t>Receita</t>
         </is>
       </c>
-      <c r="D54" s="250">
-        <f>IFERROR(VLOOKUP($B$54,#REF!,6,0)*-1,0)</f>
-        <v/>
-      </c>
-      <c r="E54" s="250">
-        <f>IFERROR(VLOOKUP($B$54,#REF!,6,0)*-1,0)</f>
-        <v/>
-      </c>
-      <c r="F54" s="250">
-        <f>IFERROR(VLOOKUP($B$54,#REF!,6,0)*-1,0)</f>
-        <v/>
+      <c r="D54" s="250" t="n">
+        <v>3102978.5</v>
+      </c>
+      <c r="E54" s="250" t="n">
+        <v>2627506.52</v>
+      </c>
+      <c r="F54" s="250" t="n">
+        <v>4861666.72</v>
       </c>
       <c r="G54" s="251">
         <f>SUM(D54:F54)</f>
@@ -5197,17 +5186,14 @@
           <t>Deduções</t>
         </is>
       </c>
-      <c r="D55" s="256">
-        <f>IFERROR(VLOOKUP($B$55,#REF!,6,0),0)</f>
-        <v/>
-      </c>
-      <c r="E55" s="256">
-        <f>IFERROR(VLOOKUP($B$55,#REF!,6,0),0)</f>
-        <v/>
-      </c>
-      <c r="F55" s="256">
-        <f>IFERROR(VLOOKUP($B$55,#REF!,6,0),0)</f>
-        <v/>
+      <c r="D55" s="256" t="n">
+        <v>736843.98</v>
+      </c>
+      <c r="E55" s="256" t="n">
+        <v>554881.52</v>
+      </c>
+      <c r="F55" s="256" t="n">
+        <v>1170558.79</v>
       </c>
       <c r="G55" s="257">
         <f>SUM(D55:F55)</f>
@@ -5243,17 +5229,14 @@
           <t>Receita Oper.</t>
         </is>
       </c>
-      <c r="D56" s="256">
-        <f>IFERROR(VLOOKUP($B$56,#REF!,6,0)*-1,0)</f>
-        <v/>
-      </c>
-      <c r="E56" s="256">
-        <f>IFERROR(VLOOKUP($B$56,#REF!,6,0)*-1,0)</f>
-        <v/>
-      </c>
-      <c r="F56" s="256">
-        <f>IFERROR(VLOOKUP($B$56,#REF!,6,0)*-1,0)</f>
-        <v/>
+      <c r="D56" s="256" t="n">
+        <v>13736.81</v>
+      </c>
+      <c r="E56" s="256" t="n">
+        <v>12574.16</v>
+      </c>
+      <c r="F56" s="256" t="n">
+        <v>8079.5</v>
       </c>
       <c r="G56" s="257">
         <f>SUM(D56:F56)</f>
@@ -5290,10 +5273,11 @@
         <f>IFERROR((VLOOKUP($B$57,#REF!,6,0)*-1)-D58,0)</f>
         <v/>
       </c>
-      <c r="E57" s="256" t="n"/>
-      <c r="F57" s="256">
-        <f>IFERROR((VLOOKUP($B$57,#REF!,6,0)*-1)-F58,0)</f>
-        <v/>
+      <c r="E57" s="256" t="n">
+        <v>242409.14</v>
+      </c>
+      <c r="F57" s="256" t="n">
+        <v>0</v>
       </c>
       <c r="G57" s="257">
         <f>SUM(D57:F57)</f>
@@ -5361,17 +5345,14 @@
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D59" s="258">
-        <f>IFERROR(VLOOKUP($B$59,#REF!,6,0),0)</f>
-        <v/>
-      </c>
-      <c r="E59" s="258">
-        <f>IFERROR(VLOOKUP($B$59,#REF!,6,0),0)</f>
-        <v/>
-      </c>
-      <c r="F59" s="258">
-        <f>IFERROR(VLOOKUP($B$59,#REF!,6,0),0)</f>
-        <v/>
+      <c r="D59" s="258" t="n">
+        <v>232519.77</v>
+      </c>
+      <c r="E59" s="258" t="n">
+        <v>178010.62</v>
+      </c>
+      <c r="F59" s="258" t="n">
+        <v>927997.51</v>
       </c>
       <c r="G59" s="257">
         <f>SUM(D59:F59)</f>
@@ -5403,9 +5384,15 @@
           <t>CMV</t>
         </is>
       </c>
-      <c r="D60" s="256" t="n"/>
-      <c r="E60" s="256" t="n"/>
-      <c r="F60" s="256" t="n"/>
+      <c r="D60" s="256" t="n">
+        <v>1678159.06</v>
+      </c>
+      <c r="E60" s="256" t="n">
+        <v>1415075.36</v>
+      </c>
+      <c r="F60" s="256" t="n">
+        <v>2650275.19</v>
+      </c>
       <c r="G60" s="257">
         <f>SUM(D60:F60)</f>
         <v/>
@@ -5598,7 +5585,9 @@
           <t>IR Retido</t>
         </is>
       </c>
-      <c r="J66" s="165" t="n"/>
+      <c r="J66" s="165" t="n">
+        <v>2718.11</v>
+      </c>
       <c r="K66" s="121" t="inlineStr">
         <is>
           <t>CS Retido</t>
@@ -5651,17 +5640,14 @@
           <t>Estoque Contábil</t>
         </is>
       </c>
-      <c r="D68" s="256">
-        <f>IFERROR(VLOOKUP($B$68,#REF!,7,0),0)</f>
-        <v/>
-      </c>
-      <c r="E68" s="256">
-        <f>IFERROR(VLOOKUP(B68,#REF!,7,0),0)</f>
-        <v/>
-      </c>
-      <c r="F68" s="256">
-        <f>IFERROR(VLOOKUP(B68,#REF!,7,0),0)</f>
-        <v/>
+      <c r="D68" s="256" t="n">
+        <v>2921910.98</v>
+      </c>
+      <c r="E68" s="256" t="n">
+        <v>6369494.4</v>
+      </c>
+      <c r="F68" s="256" t="n">
+        <v>6061532.9</v>
       </c>
       <c r="G68" s="266">
         <f>F68</f>
@@ -5854,17 +5840,14 @@
           <t>Lucro/Prejuízo Acumulado</t>
         </is>
       </c>
-      <c r="D76" s="284">
-        <f>G42</f>
-        <v/>
-      </c>
-      <c r="E76" s="256">
-        <f>D79</f>
-        <v/>
-      </c>
-      <c r="F76" s="256">
-        <f>E79</f>
-        <v/>
+      <c r="D76" s="284" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="256" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="256" t="n">
+        <v>0</v>
       </c>
       <c r="G76" s="256">
         <f>D76</f>
@@ -5932,17 +5915,14 @@
           <t>(-) Lucro distribuído no período</t>
         </is>
       </c>
-      <c r="D78" s="268">
-        <f>IFERROR(VLOOKUP($B$78,#REF!,6,0),0)</f>
-        <v/>
-      </c>
-      <c r="E78" s="268">
-        <f>IFERROR(VLOOKUP(B78,#REF!,6,0),0)</f>
-        <v/>
-      </c>
-      <c r="F78" s="268">
-        <f>IFERROR(VLOOKUP(B78,#REF!,6,0),0)</f>
-        <v/>
+      <c r="D78" s="268" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E78" s="268" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F78" s="268" t="n">
+        <v>100000</v>
       </c>
       <c r="G78" s="269">
         <f>SUM(D78:F78)</f>
@@ -7141,17 +7121,14 @@
           <t>Receita</t>
         </is>
       </c>
-      <c r="D128" s="250">
-        <f>IFERROR(VLOOKUP($B$128,#REF!,6,0)*-1,0)</f>
-        <v/>
-      </c>
-      <c r="E128" s="250">
-        <f>IFERROR(VLOOKUP($B$128,#REF!,6,0)*-1,0)</f>
-        <v/>
-      </c>
-      <c r="F128" s="250">
-        <f>IFERROR(VLOOKUP($B$128,#REF!,6,0)*-1,0)</f>
-        <v/>
+      <c r="D128" s="250" t="n">
+        <v>2627506.52</v>
+      </c>
+      <c r="E128" s="250" t="n">
+        <v>3102978.5</v>
+      </c>
+      <c r="F128" s="250" t="n">
+        <v>4861666.72</v>
       </c>
       <c r="G128" s="251">
         <f>SUM(D128:F128)</f>
@@ -7187,17 +7164,14 @@
           <t>Deduções</t>
         </is>
       </c>
-      <c r="D129" s="256">
-        <f>IFERROR(VLOOKUP($B$129,#REF!,6,0),0)</f>
-        <v/>
-      </c>
-      <c r="E129" s="256">
-        <f>IFERROR(VLOOKUP($B$129,#REF!,6,0),0)</f>
-        <v/>
-      </c>
-      <c r="F129" s="256">
-        <f>IFERROR(VLOOKUP($B$129,#REF!,6,0),0)</f>
-        <v/>
+      <c r="D129" s="256" t="n">
+        <v>554881.52</v>
+      </c>
+      <c r="E129" s="256" t="n">
+        <v>736843.98</v>
+      </c>
+      <c r="F129" s="256" t="n">
+        <v>1170558.79</v>
       </c>
       <c r="G129" s="257">
         <f>SUM(D129:F129)</f>
@@ -7233,17 +7207,14 @@
           <t>Receita Oper.</t>
         </is>
       </c>
-      <c r="D130" s="256">
-        <f>IFERROR(VLOOKUP($B$130,#REF!,6,0)*-1,0)</f>
-        <v/>
-      </c>
-      <c r="E130" s="256">
-        <f>IFERROR(VLOOKUP($B$130,#REF!,6,0)*-1,0)</f>
-        <v/>
-      </c>
-      <c r="F130" s="256">
-        <f>IFERROR(VLOOKUP($B$130,#REF!,6,0)*-1,0)</f>
-        <v/>
+      <c r="D130" s="256" t="n">
+        <v>12574.16</v>
+      </c>
+      <c r="E130" s="256" t="n">
+        <v>13736.81</v>
+      </c>
+      <c r="F130" s="256" t="n">
+        <v>8079.5</v>
       </c>
       <c r="G130" s="257">
         <f>SUM(D130:F130)</f>
@@ -7279,17 +7250,15 @@
           <t>Outras Receitas</t>
         </is>
       </c>
-      <c r="D131" s="256">
-        <f>IFERROR((VLOOKUP($B$131,#REF!,6,0)*-1)-D132,0)</f>
-        <v/>
+      <c r="D131" s="256" t="n">
+        <v>242409.14</v>
       </c>
       <c r="E131" s="256">
         <f>IFERROR((VLOOKUP($B$131,#REF!,6,0)*-1)-E132,0)</f>
         <v/>
       </c>
-      <c r="F131" s="256">
-        <f>IFERROR((VLOOKUP($B$131,#REF!,6,0)*-1)-F132,0)</f>
-        <v/>
+      <c r="F131" s="256" t="n">
+        <v>0</v>
       </c>
       <c r="G131" s="257">
         <f>SUM(D131:F131)</f>
@@ -7360,17 +7329,14 @@
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D133" s="258">
-        <f>IFERROR(VLOOKUP($B$133,#REF!,6,0),0)</f>
-        <v/>
-      </c>
-      <c r="E133" s="258">
-        <f>IFERROR(VLOOKUP($B$133,#REF!,6,0),0)</f>
-        <v/>
-      </c>
-      <c r="F133" s="258">
-        <f>IFERROR(VLOOKUP($B$133,#REF!,6,0),0)</f>
-        <v/>
+      <c r="D133" s="258" t="n">
+        <v>178010.62</v>
+      </c>
+      <c r="E133" s="258" t="n">
+        <v>232519.77</v>
+      </c>
+      <c r="F133" s="258" t="n">
+        <v>927997.51</v>
       </c>
       <c r="G133" s="257">
         <f>SUM(D133:F133)</f>
@@ -7402,17 +7368,14 @@
           <t>CMV</t>
         </is>
       </c>
-      <c r="D134" s="256">
-        <f>IFERROR(VLOOKUP($B$134,#REF!,6,0),0)</f>
-        <v/>
-      </c>
-      <c r="E134" s="256">
-        <f>IFERROR(VLOOKUP($B$134,#REF!,6,0),0)</f>
-        <v/>
-      </c>
-      <c r="F134" s="256">
-        <f>IFERROR(VLOOKUP($B$134,#REF!,6,0),0)</f>
-        <v/>
+      <c r="D134" s="256" t="n">
+        <v>1415075.36</v>
+      </c>
+      <c r="E134" s="256" t="n">
+        <v>1678159.06</v>
+      </c>
+      <c r="F134" s="256" t="n">
+        <v>2650275.19</v>
       </c>
       <c r="G134" s="257">
         <f>SUM(D134:F134)</f>
@@ -7606,7 +7569,9 @@
           <t>IR Retido</t>
         </is>
       </c>
-      <c r="J140" s="122" t="n"/>
+      <c r="J140" s="122" t="n">
+        <v>1893.23</v>
+      </c>
       <c r="K140" s="121" t="inlineStr">
         <is>
           <t>CS Retido</t>
@@ -7659,17 +7624,14 @@
           <t>Estoque Contábil</t>
         </is>
       </c>
-      <c r="D142" s="256">
-        <f>IFERROR(VLOOKUP($B$142,#REF!,7,0),0)</f>
-        <v/>
-      </c>
-      <c r="E142" s="256">
-        <f>IFERROR(VLOOKUP(B142,#REF!,7,0),0)</f>
-        <v/>
-      </c>
-      <c r="F142" s="256">
-        <f>IFERROR(VLOOKUP(B142,#REF!,7,0),0)</f>
-        <v/>
+      <c r="D142" s="256" t="n">
+        <v>6369494.4</v>
+      </c>
+      <c r="E142" s="256" t="n">
+        <v>2921910.98</v>
+      </c>
+      <c r="F142" s="256" t="n">
+        <v>6061532.9</v>
       </c>
       <c r="G142" s="266">
         <f>F142</f>
@@ -7862,17 +7824,14 @@
           <t>Lucro/Prejuízo Acumulado</t>
         </is>
       </c>
-      <c r="D150" s="284">
-        <f>G116</f>
-        <v/>
-      </c>
-      <c r="E150" s="256">
-        <f>D153</f>
-        <v/>
-      </c>
-      <c r="F150" s="256">
-        <f>E153</f>
-        <v/>
+      <c r="D150" s="284" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" s="256" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" s="256" t="n">
+        <v>0</v>
       </c>
       <c r="G150" s="269">
         <f>D150</f>
@@ -7940,17 +7899,14 @@
           <t>(-) Lucro distribuído no período</t>
         </is>
       </c>
-      <c r="D152" s="268">
-        <f>IFERROR(VLOOKUP($B$152,#REF!,6,0),0)</f>
-        <v/>
-      </c>
-      <c r="E152" s="268">
-        <f>IFERROR(VLOOKUP(B152,#REF!,6,0),0)</f>
-        <v/>
-      </c>
-      <c r="F152" s="268">
-        <f>IFERROR(VLOOKUP(B152,#REF!,6,0),0)</f>
-        <v/>
+      <c r="D152" s="268" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E152" s="268" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F152" s="268" t="n">
+        <v>100000</v>
       </c>
       <c r="G152" s="269">
         <f>SUM(D152:F152)</f>

--- a/modelo_preenchido.xlsx
+++ b/modelo_preenchido.xlsx
@@ -1110,6 +1110,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="56"/>
       </left>
@@ -1133,19 +1146,6 @@
         <color indexed="64"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1568,6 +1568,12 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1580,65 +1586,74 @@
     <xf numFmtId="4" fontId="2" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="4" fontId="2" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="11" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
@@ -1649,12 +1664,6 @@
     <xf numFmtId="0" fontId="22" fillId="11" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="11" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1672,15 +1681,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="11" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="6"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="6"/>
@@ -1758,7 +1758,7 @@
     <xf numFmtId="164" fontId="38" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="168" fontId="38" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="6"/>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1884,7 +1884,7 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3969,7 +3969,7 @@
       <c r="B4" s="239" t="n"/>
       <c r="D4" s="240" t="n"/>
       <c r="E4" s="33" t="n"/>
-      <c r="F4" s="211" t="inlineStr">
+      <c r="F4" s="209" t="inlineStr">
         <is>
           <t>ACOMPANHAMENTO DE RESULTADO CONTÁBIL</t>
         </is>
@@ -4001,7 +4001,7 @@
       <c r="B7" s="239" t="n"/>
       <c r="D7" s="240" t="n"/>
       <c r="E7" s="33" t="n"/>
-      <c r="F7" s="212" t="inlineStr">
+      <c r="F7" s="210" t="inlineStr">
         <is>
           <t>NIT JET CENTER LTDA</t>
         </is>
@@ -4014,7 +4014,7 @@
       <c r="C8" s="242" t="n"/>
       <c r="D8" s="243" t="n"/>
       <c r="E8" s="33" t="n"/>
-      <c r="F8" s="212" t="inlineStr">
+      <c r="F8" s="210" t="inlineStr">
         <is>
           <t>CNPJ 14.051.540/0001-09</t>
         </is>
@@ -4023,7 +4023,7 @@
       <c r="M8" s="32" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="213" t="n"/>
+      <c r="B9" s="211" t="n"/>
       <c r="M9" s="32" t="n"/>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -4112,7 +4112,7 @@
         </is>
       </c>
       <c r="J16" s="248" t="n"/>
-      <c r="K16" s="194" t="inlineStr">
+      <c r="K16" s="190" t="inlineStr">
         <is>
           <t>CSLL</t>
         </is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="J31" s="248" t="n"/>
-      <c r="K31" s="197">
+      <c r="K31" s="212">
         <f>J30+L30</f>
         <v/>
       </c>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="J32" s="248" t="n"/>
-      <c r="K32" s="192">
+      <c r="K32" s="194">
         <f>G25-J27-J28-L27</f>
         <v/>
       </c>
@@ -4751,13 +4751,13 @@
           <t>Acompanhamento de Lucro à Distribuir</t>
         </is>
       </c>
-      <c r="I36" s="194" t="inlineStr">
+      <c r="I36" s="190" t="inlineStr">
         <is>
           <t>IRPJ_1º Trimestre</t>
         </is>
       </c>
       <c r="J36" s="249" t="n"/>
-      <c r="K36" s="195" t="inlineStr">
+      <c r="K36" s="191" t="inlineStr">
         <is>
           <t>CSLL_1º Trimestre</t>
         </is>
@@ -4792,18 +4792,18 @@
     </row>
     <row r="38" ht="17" customHeight="1" thickBot="1" thickTop="1">
       <c r="B38" s="170" t="n"/>
-      <c r="C38" s="194" t="n"/>
-      <c r="D38" s="194" t="inlineStr">
+      <c r="C38" s="190" t="n"/>
+      <c r="D38" s="190" t="inlineStr">
         <is>
           <t>JANEIRO</t>
         </is>
       </c>
-      <c r="E38" s="195" t="inlineStr">
+      <c r="E38" s="191" t="inlineStr">
         <is>
           <t>FEVEREIRO</t>
         </is>
       </c>
-      <c r="F38" s="195" t="inlineStr">
+      <c r="F38" s="191" t="inlineStr">
         <is>
           <t>MARÇO</t>
         </is>
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="J53" s="248" t="n"/>
-      <c r="K53" s="194" t="inlineStr">
+      <c r="K53" s="190" t="inlineStr">
         <is>
           <t>CSLL</t>
         </is>
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="J68" s="248" t="n"/>
-      <c r="K68" s="192">
+      <c r="K68" s="194">
         <f>J67+L67</f>
         <v/>
       </c>
@@ -5687,7 +5687,7 @@
         </is>
       </c>
       <c r="J69" s="248" t="n"/>
-      <c r="K69" s="192">
+      <c r="K69" s="194">
         <f>G62-J64-J65-L64</f>
         <v/>
       </c>
@@ -5750,13 +5750,13 @@
           <t>Acompanhamento de Lucro à Distribuir</t>
         </is>
       </c>
-      <c r="I73" s="194" t="inlineStr">
+      <c r="I73" s="190" t="inlineStr">
         <is>
           <t>IRPJ_2º Trimestre</t>
         </is>
       </c>
       <c r="J73" s="249" t="n"/>
-      <c r="K73" s="195" t="inlineStr">
+      <c r="K73" s="191" t="inlineStr">
         <is>
           <t>CSLL_2º Trimestre</t>
         </is>
@@ -5791,7 +5791,7 @@
     </row>
     <row r="75" ht="17" customHeight="1" thickBot="1" thickTop="1">
       <c r="B75" s="170" t="n"/>
-      <c r="C75" s="194" t="n"/>
+      <c r="C75" s="190" t="n"/>
       <c r="D75" s="24" t="inlineStr">
         <is>
           <t>ABRIL</t>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="J90" s="248" t="n"/>
-      <c r="K90" s="194" t="inlineStr">
+      <c r="K90" s="190" t="inlineStr">
         <is>
           <t>CSLL</t>
         </is>
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="J105" s="248" t="n"/>
-      <c r="K105" s="192">
+      <c r="K105" s="194">
         <f>J104+L104</f>
         <v/>
       </c>
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="J106" s="248" t="n"/>
-      <c r="K106" s="192">
+      <c r="K106" s="194">
         <f>G99-J101-J102-L101</f>
         <v/>
       </c>
@@ -6743,13 +6743,13 @@
           <t>Acompanhamento de Lucro à Distribuir</t>
         </is>
       </c>
-      <c r="I110" s="194" t="inlineStr">
+      <c r="I110" s="190" t="inlineStr">
         <is>
           <t>IRPJ_3º Trimestre</t>
         </is>
       </c>
       <c r="J110" s="249" t="n"/>
-      <c r="K110" s="195" t="inlineStr">
+      <c r="K110" s="191" t="inlineStr">
         <is>
           <t>CSLL_3º Trimestre</t>
         </is>
@@ -6784,7 +6784,7 @@
     </row>
     <row r="112" ht="17" customHeight="1" thickBot="1" thickTop="1">
       <c r="B112" s="170" t="n"/>
-      <c r="C112" s="194" t="n"/>
+      <c r="C112" s="190" t="n"/>
       <c r="D112" s="24" t="inlineStr">
         <is>
           <t>JULHO</t>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="J127" s="248" t="n"/>
-      <c r="K127" s="194" t="inlineStr">
+      <c r="K127" s="190" t="inlineStr">
         <is>
           <t>CSLL</t>
         </is>
@@ -7644,7 +7644,7 @@
         </is>
       </c>
       <c r="J142" s="248" t="n"/>
-      <c r="K142" s="192">
+      <c r="K142" s="194">
         <f>J141+L141</f>
         <v/>
       </c>
@@ -7671,7 +7671,7 @@
         </is>
       </c>
       <c r="J143" s="248" t="n"/>
-      <c r="K143" s="192">
+      <c r="K143" s="194">
         <f>G136-J138-J139-L138</f>
         <v/>
       </c>
@@ -7734,13 +7734,13 @@
           <t>Acompanhamento de Lucro à Distribuir</t>
         </is>
       </c>
-      <c r="I147" s="194" t="inlineStr">
+      <c r="I147" s="190" t="inlineStr">
         <is>
           <t>IRPJ_4º TRIMESTRE</t>
         </is>
       </c>
       <c r="J147" s="249" t="n"/>
-      <c r="K147" s="195" t="inlineStr">
+      <c r="K147" s="191" t="inlineStr">
         <is>
           <t>CSLL_4º TRIMESTRE</t>
         </is>
@@ -7775,7 +7775,7 @@
     </row>
     <row r="149" ht="17" customHeight="1" thickBot="1" thickTop="1">
       <c r="B149" s="170" t="n"/>
-      <c r="C149" s="194" t="n"/>
+      <c r="C149" s="190" t="n"/>
       <c r="D149" s="24" t="inlineStr">
         <is>
           <t>OUTUBRO</t>
@@ -8020,64 +8020,64 @@
   </sheetData>
   <mergeCells count="61">
     <mergeCell ref="K16:L16"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="I90:J90"/>
+    <mergeCell ref="I105:J105"/>
+    <mergeCell ref="K68:L68"/>
     <mergeCell ref="B86:M86"/>
-    <mergeCell ref="K68:L68"/>
-    <mergeCell ref="I90:J90"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="I105:J105"/>
     <mergeCell ref="I88:L88"/>
+    <mergeCell ref="I51:L51"/>
     <mergeCell ref="K142:L142"/>
-    <mergeCell ref="I51:L51"/>
     <mergeCell ref="F8:K8"/>
+    <mergeCell ref="I36:J36"/>
     <mergeCell ref="C14:G14"/>
-    <mergeCell ref="I36:J36"/>
     <mergeCell ref="K36:L36"/>
     <mergeCell ref="F4:K5"/>
     <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C64:G64"/>
     <mergeCell ref="K110:L110"/>
-    <mergeCell ref="C64:G64"/>
     <mergeCell ref="I106:J106"/>
     <mergeCell ref="C73:G73"/>
-    <mergeCell ref="K127:L127"/>
+    <mergeCell ref="I16:J16"/>
     <mergeCell ref="C147:G147"/>
-    <mergeCell ref="I16:J16"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="I147:J147"/>
     <mergeCell ref="K32:L32"/>
     <mergeCell ref="I34:L34"/>
+    <mergeCell ref="B12:M12"/>
     <mergeCell ref="K90:L90"/>
     <mergeCell ref="I108:L108"/>
+    <mergeCell ref="K106:L106"/>
+    <mergeCell ref="K31:L31"/>
     <mergeCell ref="I53:J53"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="K106:L106"/>
     <mergeCell ref="B49:M49"/>
     <mergeCell ref="I127:J127"/>
     <mergeCell ref="I143:J143"/>
+    <mergeCell ref="K105:L105"/>
+    <mergeCell ref="I68:J68"/>
     <mergeCell ref="I145:L145"/>
-    <mergeCell ref="I68:J68"/>
-    <mergeCell ref="K105:L105"/>
-    <mergeCell ref="I69:J69"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="B123:M123"/>
+    <mergeCell ref="C27:G27"/>
     <mergeCell ref="C138:G138"/>
-    <mergeCell ref="B123:M123"/>
+    <mergeCell ref="B3:D8"/>
     <mergeCell ref="I142:J142"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="B3:D8"/>
-    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C36:G36"/>
     <mergeCell ref="I125:L125"/>
-    <mergeCell ref="C36:G36"/>
     <mergeCell ref="C110:G110"/>
     <mergeCell ref="B9:L9"/>
     <mergeCell ref="I110:J110"/>
+    <mergeCell ref="K53:L53"/>
     <mergeCell ref="I73:J73"/>
-    <mergeCell ref="K53:L53"/>
     <mergeCell ref="K73:L73"/>
     <mergeCell ref="I71:L71"/>
     <mergeCell ref="C125:G125"/>
     <mergeCell ref="K147:L147"/>
+    <mergeCell ref="I31:J31"/>
     <mergeCell ref="F7:K7"/>
-    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I69:J69"/>
     <mergeCell ref="K69:L69"/>
-    <mergeCell ref="B12:M12"/>
+    <mergeCell ref="K127:L127"/>
     <mergeCell ref="C101:G101"/>
     <mergeCell ref="K143:L143"/>
   </mergeCells>
@@ -9830,29 +9830,29 @@
   <sheetData>
     <row r="1" ht="6.75" customHeight="1"/>
     <row r="2" ht="7.5" customHeight="1">
-      <c r="B2" s="225" t="n"/>
+      <c r="B2" s="216" t="n"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="B3" s="226" t="inlineStr">
+      <c r="B3" s="217" t="inlineStr">
         <is>
           <t>CONFRONTOS 2023 - APURAÇÕES VS DECLARAÇÕES_IRPJ E CSLL</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="B4" s="227">
+      <c r="B4" s="218">
         <f>Acomp.Resultado_2024!F7</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="227">
+      <c r="B5" s="218">
         <f>Acomp.Resultado_2024!F8</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="7.5" customHeight="1">
-      <c r="B6" s="226" t="n"/>
+      <c r="B6" s="217" t="n"/>
     </row>
     <row r="7" ht="6" customHeight="1" thickBot="1"/>
     <row r="8" ht="16" customHeight="1" thickBot="1">
@@ -9885,7 +9885,7 @@
         </is>
       </c>
       <c r="J8" s="287" t="n"/>
-      <c r="K8" s="217" t="inlineStr">
+      <c r="K8" s="214" t="inlineStr">
         <is>
           <t>TOTAL 2023</t>
         </is>
@@ -10533,19 +10533,19 @@
   <mergeCells count="16">
     <mergeCell ref="B4:K4"/>
     <mergeCell ref="C8:D8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="B36:K36"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="B35:K35"/>
     <mergeCell ref="G27:H27"/>
     <mergeCell ref="E27:F27"/>
     <mergeCell ref="I27:J27"/>
+    <mergeCell ref="B6:K6"/>
     <mergeCell ref="B2:K2"/>
-    <mergeCell ref="B6:K6"/>
-    <mergeCell ref="I8:J8"/>
     <mergeCell ref="G8:H8"/>
-    <mergeCell ref="B5:K5"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="B3:K3"/>
-    <mergeCell ref="B36:K36"/>
+    <mergeCell ref="B5:K5"/>
     <mergeCell ref="B37:K37"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
